--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:50:04+00:00</t>
+    <t>2025-02-13T14:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MOPEDEncounter#Encounter.admission</t>
+    <t>element:http://example.org/StructureDefinition/MopedEncounter#Encounter.admission</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/moped-ext-aufnahmeart</t>
+    <t>https://elga.moped.at/StructureDefinition/moped-ext-aufnahmeart</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MopedEncounter#Encounter.admission</t>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedEncounter#Encounter.admission</t>
   </si>
   <si>
     <t>ID</t>
@@ -341,7 +341,7 @@
     <t>Code für die Art der Aufnahme</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-aufnahmeart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/AufnahmeartVS</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -687,7 +687,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="29.20703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.01171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-aufnahmeart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
